--- a/resources/HEARTH_Call_Sheet_Template.xlsx
+++ b/resources/HEARTH_Call_Sheet_Template.xlsx
@@ -208,7 +208,7 @@
     <t xml:space="preserve">SPECIAL INSTRUCTIONS &amp; NOTES</t>
   </si>
   <si>
-    <t xml:space="preserve">HEARTH  ·  Where Stories Gather  ·  hearthmedia.com  ·  This call sheet is confidential. Do not distribute beyond the production.</t>
+    <t xml:space="preserve">HEARTH  ·  Production Resource Library  ·  buildyourhearth.studio  ·  This call sheet is confidential. Do not distribute beyond the production.</t>
   </si>
 </sst>
 </file>

--- a/resources/HEARTH_Call_Sheet_Template.xlsx
+++ b/resources/HEARTH_Call_Sheet_Template.xlsx
@@ -208,7 +208,7 @@
     <t xml:space="preserve">SPECIAL INSTRUCTIONS &amp; NOTES</t>
   </si>
   <si>
-    <t xml:space="preserve">HEARTH  ·  Production Resource Library  ·  buildyourhearth.studio  ·  This call sheet is confidential. Do not distribute beyond the production.</t>
+    <t xml:space="preserve">HEARTH  ·  Where Stories Gather  ·  hearthmedia.com  ·  This call sheet is confidential. Do not distribute beyond the production.</t>
   </si>
 </sst>
 </file>
